--- a/artfynd/A 62724-2023 artfynd.xlsx
+++ b/artfynd/A 62724-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122128407</v>
+        <v>122128271</v>
       </c>
       <c r="B2" t="n">
         <v>57916</v>
@@ -708,17 +708,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östra Genastorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>438143</v>
+        <v>438175</v>
       </c>
       <c r="R2" t="n">
-        <v>6243584</v>
+        <v>6243588</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +764,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emil Lundahl</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122128271</v>
+        <v>122128407</v>
       </c>
       <c r="B3" t="n">
         <v>57916</v>
@@ -814,36 +833,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östra Genastorp, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438175</v>
+        <v>438143</v>
       </c>
       <c r="R3" t="n">
-        <v>6243588</v>
+        <v>6243584</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +895,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Emil Lundahl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 62724-2023 artfynd.xlsx
+++ b/artfynd/A 62724-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122128271</v>
       </c>
       <c r="B2" t="n">
-        <v>57916</v>
+        <v>57921</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>122128407</v>
       </c>
       <c r="B3" t="n">
-        <v>57916</v>
+        <v>57921</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 62724-2023 artfynd.xlsx
+++ b/artfynd/A 62724-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122128271</v>
+        <v>122128407</v>
       </c>
       <c r="B2" t="n">
         <v>57921</v>
@@ -708,36 +708,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östra Genastorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>438175</v>
+        <v>438143</v>
       </c>
       <c r="R2" t="n">
-        <v>6243588</v>
+        <v>6243584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Emil Lundahl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122128407</v>
+        <v>122128271</v>
       </c>
       <c r="B3" t="n">
         <v>57921</v>
@@ -833,17 +814,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östra Genastorp, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438143</v>
+        <v>438175</v>
       </c>
       <c r="R3" t="n">
-        <v>6243584</v>
+        <v>6243588</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +895,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Lundahl</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 62724-2023 artfynd.xlsx
+++ b/artfynd/A 62724-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122128407</v>
+        <v>122128271</v>
       </c>
       <c r="B2" t="n">
         <v>57921</v>
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>102990</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Järnsparv</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Prunella modularis</t>
@@ -708,17 +703,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östra Genastorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>438143</v>
+        <v>438175</v>
       </c>
       <c r="R2" t="n">
-        <v>6243584</v>
+        <v>6243588</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +759,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,7 +784,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emil Lundahl</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,7 +795,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122128271</v>
+        <v>122128407</v>
       </c>
       <c r="B3" t="n">
         <v>57921</v>
@@ -799,11 +813,6 @@
       <c r="E3" t="n">
         <v>102990</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Järnsparv</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Prunella modularis</t>
@@ -814,36 +823,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östra Genastorp, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438175</v>
+        <v>438143</v>
       </c>
       <c r="R3" t="n">
-        <v>6243588</v>
+        <v>6243584</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Emil Lundahl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 62724-2023 artfynd.xlsx
+++ b/artfynd/A 62724-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122128271</v>
+        <v>122128407</v>
       </c>
       <c r="B2" t="n">
-        <v>57921</v>
+        <v>57925</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -693,6 +693,11 @@
       <c r="E2" t="n">
         <v>102990</v>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Prunella modularis</t>
@@ -703,36 +708,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östra Genastorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>438175</v>
+        <v>438143</v>
       </c>
       <c r="R2" t="n">
-        <v>6243588</v>
+        <v>6243584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Emil Lundahl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -795,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122128407</v>
+        <v>122128271</v>
       </c>
       <c r="B3" t="n">
-        <v>57921</v>
+        <v>57925</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,6 +799,11 @@
       <c r="E3" t="n">
         <v>102990</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Prunella modularis</t>
@@ -823,17 +814,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östra Genastorp, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438143</v>
+        <v>438175</v>
       </c>
       <c r="R3" t="n">
-        <v>6243584</v>
+        <v>6243588</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +895,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emil Lundahl</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 62724-2023 artfynd.xlsx
+++ b/artfynd/A 62724-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122128407</v>
+        <v>122128271</v>
       </c>
       <c r="B2" t="n">
         <v>57925</v>
@@ -708,17 +708,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östra Genastorp, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>438143</v>
+        <v>438175</v>
       </c>
       <c r="R2" t="n">
-        <v>6243584</v>
+        <v>6243588</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +764,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emil Lundahl</t>
+          <t>Frida Nettelbladt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122128271</v>
+        <v>122128407</v>
       </c>
       <c r="B3" t="n">
         <v>57925</v>
@@ -814,36 +833,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östra Genastorp, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438175</v>
+        <v>438143</v>
       </c>
       <c r="R3" t="n">
-        <v>6243588</v>
+        <v>6243584</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +895,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frida Nettelbladt</t>
+          <t>Emil Lundahl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
